--- a/examples/templates/branddocs_template.xlsx
+++ b/examples/templates/branddocs_template.xlsx
@@ -168,7 +168,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -195,11 +195,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
@@ -1229,7 +1237,16 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1510,7 +1527,7 @@
           <t>Unit price (input)</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="17">
         <f>Inputs!B5</f>
         <v/>
       </c>
@@ -1521,7 +1538,7 @@
           <t>Implied gross</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="17">
         <f>Inputs!B4*Inputs!B5</f>
         <v/>
       </c>
@@ -1532,7 +1549,7 @@
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="18">
         <f>IF(B7=0,0,B4/B7)</f>
         <v/>
       </c>
@@ -1576,14 +1593,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Executive Dashboard</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Formula-backed snapshot generated from the model, inputs, and summary tabs</t>
         </is>
@@ -1612,19 +1629,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19">
+      <c r="A5" s="21">
         <f>Summary!B4</f>
         <v/>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="22">
         <f>Summary!B8</f>
         <v/>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="21">
         <f>Summary!B5</f>
         <v/>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="23">
         <f>Scenarios!B3</f>
         <v/>
       </c>
@@ -1797,10 +1814,10 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="18" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1815,10 +1832,10 @@
           <t>Upside</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="24" t="n">
         <v>1.12</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="18" t="n">
         <v>0.025</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1833,10 +1850,10 @@
           <t>Downside</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="24" t="n">
         <v>0.91</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="18" t="n">
         <v>-0.035</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1935,7 +1952,7 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D2" s="23" t="n">
+      <c r="D2" s="25" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -1955,7 +1972,7 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="D3" s="23" t="n">
+      <c r="D3" s="25" t="n">
         <v>9800</v>
       </c>
     </row>
@@ -1975,7 +1992,7 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D4" s="23" t="n">
+      <c r="D4" s="25" t="n">
         <v>14200</v>
       </c>
     </row>

--- a/examples/templates/branddocs_template.xlsx
+++ b/examples/templates/branddocs_template.xlsx
@@ -27,8 +27,13 @@
     <definedName name="report_title">'Cover'!$A$1</definedName>
     <definedName name="scenario_block">'Scenarios'!$A$5:$D$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Model'!$A$1:$G$27</definedName>
+    <definedName name="q_total" localSheetId="2">Model!$F$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Model'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Model'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Summary'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Dashboard'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Dashboard'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Scenarios'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Scenarios'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,15 +42,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_($* #,##0.00_);_($* (#,##0.00);_($* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="#,##0;[Red](#,##0)"/>
+    <numFmt numFmtId="166" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="#,##0;[Red](#,##0)"/>
+    <numFmt numFmtId="170" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="171" formatCode="#,##0 &quot;bps&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,15 +90,32 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF2B7CD3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF16213F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="FF2B7CD3"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <color rgb="FF16213F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF16213F"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -130,7 +154,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -153,8 +177,13 @@
         <color rgb="FF16213F"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF16213F"/>
+      </top>
+    </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -168,14 +197,23 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
@@ -192,10 +230,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="9"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="5">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -207,11 +250,13 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="8"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="8"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -221,10 +266,12 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
     <cellStyle name="BrandDocsTitle" xfId="1" hidden="0"/>
     <cellStyle name="BrandDocsHeader" xfId="2" hidden="0"/>
@@ -232,8 +279,20 @@
     <cellStyle name="BrandDocsPercent" xfId="4" hidden="0"/>
     <cellStyle name="BrandDocsInput" xfId="5" hidden="0"/>
     <cellStyle name="BrandDocsKPI" xfId="6" hidden="0"/>
+    <cellStyle name="BrandDocsSubtitle" xfId="7" hidden="0"/>
+    <cellStyle name="BrandDocsTotal" xfId="8" hidden="0"/>
+    <cellStyle name="BrandDocsDate" xfId="9" hidden="0"/>
+    <cellStyle name="BrandDocsMultiple" xfId="10" hidden="0"/>
+    <cellStyle name="BrandDocsBandHeader" xfId="11" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF1FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -255,8 +314,46 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF16213F"/>
+          <bgColor rgb="FF16213F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFEAF1FF"/>
+          <bgColor rgb="FFEAF1FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF2B7CD3"/>
+          <bgColor rgb="FF2B7CD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="BrandDocsTableStyle" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -589,6 +686,66 @@
     <author>BrandDocs</author>
   </authors>
   <commentList>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic figure - pulled live from the Summary tab.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BrandDocs</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic input - replace with your data.</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic input - replace with your data.</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic input - replace with your data.</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic input - replace with your data.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BrandDocs</author>
+  </authors>
+  <commentList>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>Synthetic headline - derived from the model and inputs tabs.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BrandDocs</author>
+  </authors>
+  <commentList>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Synthetic scenario selector used by formulas and visual QA.</t>
@@ -634,7 +791,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5040000" cy="2880000"/>
@@ -679,6 +836,31 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -710,7 +892,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BrandDocsDataTbl" displayName="BrandDocsDataTbl" ref="A3:G7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BrandDocsDataTbl" displayName="BrandDocsDataTbl" ref="A3:G8" headerRowCount="1" totalsRowCount="1" totalsRowShown="1">
   <autoFilter ref="A3:G7"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Line item"/>
@@ -734,7 +916,7 @@
     <tableColumn id="3" name="Margin delta"/>
     <tableColumn id="4" name="Narrative"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="BrandDocsTableStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -743,45 +925,45 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="16213F"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="2B7CD3"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="EAF1FF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="2B7CD3"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E0742B"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="DCE7FF"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="5778B0"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="9CC0F0"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="C7912B"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="2B7CD3"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="16213F"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1027,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1136,15 +1318,48 @@
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
     </row>
+    <row r="11">
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Blue fill = editable assumptions you fill in</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Formulas</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Navy text = model formulas (do not overwrite)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1162,7 +1377,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Model Inputs</t>
         </is>
@@ -1191,7 +1406,7 @@
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="15" t="n">
         <v>29070</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -1206,7 +1421,7 @@
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="16" t="n">
         <v>50</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -1221,7 +1436,7 @@
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.12</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1236,7 +1451,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="17" t="n">
         <v>0.22</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1247,6 +1462,20 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <conditionalFormatting sqref="B4:B7">
+    <cfRule type="containsBlanks" priority="1" dxfId="0">
+      <formula>LEN(TRIM(B4))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Invalid units" error="Units sold must be a whole number greater than or equal to 0." promptTitle="Units sold" prompt="Enter the synthetic unit volume (whole number, 0 or more)." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6 B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Invalid rate" error="Rate must be a decimal between 0 and 1." promptTitle="Rate (0-1)" prompt="Enter a rate as a fraction between 0 and 1 (e.g. 0.12 for 12%)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
@@ -1256,6 +1485,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1265,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1278,7 +1508,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Revenue Model</t>
         </is>
@@ -1327,23 +1557,23 @@
           <t>Gross revenue</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="18" t="n">
         <v>320000</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="18" t="n">
         <v>351000</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>372500</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="18" t="n">
         <v>410000</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="18">
         <f>SUM(B4:E4)</f>
         <v/>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="19">
         <f>IF($F$7=0,0,F4/$F$7)</f>
         <v/>
       </c>
@@ -1354,23 +1584,23 @@
           <t>Discounts</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="20" t="n">
         <v>-38400</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="20" t="n">
         <v>-42120</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="20" t="n">
         <v>-44700</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="20" t="n">
         <v>-49200</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="20">
         <f>SUM(B5:E5)</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="19">
         <f>IF($F$7=0,0,F5/$F$7)</f>
         <v/>
       </c>
@@ -1381,23 +1611,23 @@
           <t>Returns</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <v>-9600</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <v>-10530</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="20" t="n">
         <v>-11175</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="20" t="n">
         <v>-12300</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="20">
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="19">
         <f>IF($F$7=0,0,F6/$F$7)</f>
         <v/>
       </c>
@@ -1408,39 +1638,54 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="18">
         <f>SUM(B4:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="18">
         <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="18">
         <f>SUM(D4:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="18">
         <f>SUM(E4:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="18">
         <f>SUM(B7:E7)</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="19">
         <f>IF($F$7=0,0,F7/$F$7)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F8" s="21">
+        <f>SUBTOTAL(109,F4:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Subtotal (visible)</t>
         </is>
       </c>
-      <c r="F9" s="15">
+      <c r="F10" s="22">
         <f>SUBTOTAL(9,F4:F6)</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>SUM(BrandDocsDataTbl[FY Total])</f>
         <v/>
       </c>
     </row>
@@ -1456,15 +1701,15 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" rank="3" priority="5" dxfId="0"/>
+    <cfRule type="top10" rank="3" priority="5" dxfId="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G7">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="2">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F6">
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>F4&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1479,6 +1724,14 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;D&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
@@ -1500,7 +1753,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Executive Summary</t>
         </is>
@@ -1524,7 +1777,7 @@
           <t>FY net revenue</t>
         </is>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="18">
         <f>Model!F7</f>
         <v/>
       </c>
@@ -1535,7 +1788,7 @@
           <t>Units sold (input)</t>
         </is>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="18">
         <f>Inputs!B4</f>
         <v/>
       </c>
@@ -1546,7 +1799,7 @@
           <t>Unit price (input)</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="23">
         <f>Inputs!B5</f>
         <v/>
       </c>
@@ -1557,7 +1810,7 @@
           <t>Implied gross</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="23">
         <f>Inputs!B4*Inputs!B5</f>
         <v/>
       </c>
@@ -1568,7 +1821,7 @@
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="24">
         <f>IF(B7=0,0,B4/B7)</f>
         <v/>
       </c>
@@ -1586,9 +1839,21 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B4:B8">
+    <cfRule type="top10" rank="1" priority="1" dxfId="0"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;D&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1598,13 +1863,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -1612,14 +1877,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Executive Dashboard</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Formula-backed snapshot generated from the model, inputs, and summary tabs</t>
         </is>
@@ -1648,19 +1913,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="27">
         <f>Summary!B4</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="28">
         <f>Summary!B8</f>
         <v/>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="27">
         <f>Summary!B5</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="29">
         <f>Scenarios!B3</f>
         <v/>
       </c>
@@ -1688,7 +1953,7 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="18">
         <f>Model!B7</f>
         <v/>
       </c>
@@ -1704,11 +1969,11 @@
           <t>Q2</t>
         </is>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="18">
         <f>Model!C7</f>
         <v/>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="19">
         <f>IF(B8=0,0,B9/B8-1)</f>
         <v/>
       </c>
@@ -1719,11 +1984,11 @@
           <t>Q3</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="18">
         <f>Model!D7</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="19">
         <f>IF(B9=0,0,B10/B9-1)</f>
         <v/>
       </c>
@@ -1734,13 +1999,122 @@
           <t>Q4</t>
         </is>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="18">
         <f>Model!E7</f>
         <v/>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="19">
         <f>IF(B10=0,0,B11/B10-1)</f>
         <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>KPI trends</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>QoQ / delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>272000</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>298350</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>316625</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>348500</v>
+      </c>
+      <c r="G16" s="30">
+        <f>IF(B11=0,0,B11/B8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>281000</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>305000</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>366000</v>
+      </c>
+      <c r="G17" s="31">
+        <f>ROUND((Summary!B8-0.85)*10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Active seats</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1402</v>
       </c>
     </row>
   </sheetData>
@@ -1765,9 +2139,65 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C9:C11">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;D&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSparkline" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" type="line">
+          <x14:colorSeries rgb="FF2B7CD3"/>
+          <x14:colorNegative rgb="FFE0742B"/>
+          <x14:colorMarkers rgb="FF16213F"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Dashboard!B16:E16</xm:f>
+              <xm:sqref>F16</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" type="line">
+          <x14:colorSeries rgb="FF2B7CD3"/>
+          <x14:colorNegative rgb="FFE0742B"/>
+          <x14:colorMarkers rgb="FF16213F"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Dashboard!B17:E17</xm:f>
+              <xm:sqref>F17</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" type="line">
+          <x14:colorSeries rgb="FF2B7CD3"/>
+          <x14:colorNegative rgb="FFE0742B"/>
+          <x14:colorMarkers rgb="FF16213F"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Dashboard!B18:E18</xm:f>
+              <xm:sqref>F18</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1787,7 +2217,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Scenario Controls</t>
         </is>
@@ -1833,10 +2263,10 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1851,10 +2281,10 @@
           <t>Upside</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="32" t="n">
         <v>1.12</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="24" t="n">
         <v>0.025</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1869,10 +2299,10 @@
           <t>Downside</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="32" t="n">
         <v>0.91</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="24" t="n">
         <v>-0.035</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1887,7 +2317,7 @@
           <t>Scenario revenue</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="18">
         <f>Summary!B4*INDEX(B6:B8,MATCH($B$3,A6:A8,0))</f>
         <v/>
       </c>
@@ -1898,19 +2328,30 @@
           <t>Scenario margin</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="19">
         <f>Summary!B8+INDEX(C6:C8,MATCH($B$3,A6:A8,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Upside,Downside"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Unknown scenario" error="The scenario must match one of Base / Upside / Downside." promptTitle="Scenario" prompt="Pick a scenario that exists in the scenario table below." type="custom">
+      <formula1>=COUNTIF($A$6:$A$8,$B$3)&gt;0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;D&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1971,7 +2412,7 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D2" s="26" t="n">
+      <c r="D2" s="33" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -1991,7 +2432,7 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="D3" s="26" t="n">
+      <c r="D3" s="33" t="n">
         <v>9800</v>
       </c>
     </row>
@@ -2011,22 +2452,35 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="33" t="n">
         <v>14200</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="22">
         <f>SUM(D2:D4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B4">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C4">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="0" text="Widget">
+      <formula>NOT(ISERROR(SEARCH("Widget",C2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Invalid date" error="Date must be on or after 2000-01-01." promptTitle="Transaction date" prompt="Enter the transaction date (ISO yyyy-mm-dd)." type="date" operator="greaterThanOrEqual">
+      <formula1>2000-01-01</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/templates/branddocs_template.xlsx
+++ b/examples/templates/branddocs_template.xlsx
@@ -928,7 +928,7 @@
         <a:srgbClr val="16213F"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EAF1FF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="2B7CD3"/>
@@ -946,19 +946,19 @@
         <a:srgbClr val="DCE7FF"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="5778B0"/>
+        <a:srgbClr val="E0742B"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="9CC0F0"/>
+        <a:srgbClr val="2B7CD3"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C7912B"/>
+        <a:srgbClr val="E0742B"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="2B7CD3"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="16213F"/>
+        <a:srgbClr val="E0742B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
